--- a/data/CL31-February.xlsx
+++ b/data/CL31-February.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adane\dm_tracker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4853F291-DEE9-4022-BFF0-6EAAD88EC495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25AC2256-BB78-4E35-ACA9-3C785F8A00B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7BD6478B-385B-46E3-99A0-A28036FEB319}"/>
+    <workbookView xWindow="2340" yWindow="1455" windowWidth="16575" windowHeight="14745" xr2:uid="{7BD6478B-385B-46E3-99A0-A28036FEB319}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2043,7 +2043,7 @@
   <dimension ref="A1:J342"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.5703125" customWidth="1"/>
+    <col min="1" max="1" width="59.5703125" customWidth="1"/>
     <col min="2" max="2" width="62.7109375" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>

--- a/data/CL31-February.xlsx
+++ b/data/CL31-February.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adane\dm_tracker\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9943F9D6-5BEE-4FF8-A8D7-C10EA2F8CDD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5638923-7265-4881-AE16-D094E244DE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7BD6478B-385B-46E3-99A0-A28036FEB319}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="206">
   <si>
     <t>Activity ID</t>
   </si>
@@ -101,12 +101,6 @@
     <t>MAE design complete</t>
   </si>
   <si>
-    <t xml:space="preserve">            AMP8-FPS-MAE-1110</t>
-  </si>
-  <si>
-    <t>MAE Project Start</t>
-  </si>
-  <si>
     <t xml:space="preserve">            AMP8-FPS-MAE-1120</t>
   </si>
   <si>
@@ -123,60 +117,6 @@
   </si>
   <si>
     <t>Review Information and raise RFIs/TQs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            AMP8-FPS-MAE-1070</t>
-  </si>
-  <si>
-    <t>All existing drawings in dwg format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            AMP8-FPS-MAE-1100</t>
-  </si>
-  <si>
-    <t>Catchment Area EPD (Explosion Protection Document)- Confirmation of Hazardous Substances in existing tank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            AMP8-FPS-MAE-1090</t>
-  </si>
-  <si>
-    <t>Confirmation of detention tank type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            AMP8-FPS-MAE-1080</t>
-  </si>
-  <si>
-    <t>Feasibility Control Philosophy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            AMP8-FPS-MAE-1060</t>
-  </si>
-  <si>
-    <t>Flowrate from existing shaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            AMP8-FPS-MAE-1040</t>
-  </si>
-  <si>
-    <t>GFR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            AMP8-FPS-MAE-1020</t>
-  </si>
-  <si>
-    <t>Historical as-built drawings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            AMP8-FPS-MAE-1050</t>
-  </si>
-  <si>
-    <t>Historical model?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">            AMP8-FPS-MAE-1010</t>
-  </si>
-  <si>
-    <t>Topographical data and drawing from UU</t>
   </si>
   <si>
     <t xml:space="preserve">            AMP8-FPS-MAE-1150</t>
@@ -1093,7 +1033,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D771482-B25F-4BD7-ACA7-C660D4341941}">
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.5703125" customWidth="1"/>
@@ -1101,6 +1041,8 @@
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="23.140625" customWidth="1"/>
     <col min="5" max="5" width="23.28515625" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1279,13 +1221,19 @@
         <v>22</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D7" s="1">
         <v>46043</v>
       </c>
+      <c r="E7" s="1">
+        <v>46050</v>
+      </c>
       <c r="F7" s="1">
         <v>46043</v>
+      </c>
+      <c r="G7" s="1">
+        <v>46050</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1302,25 +1250,19 @@
         <v>24</v>
       </c>
       <c r="C8">
-        <v>6</v>
-      </c>
-      <c r="D8" s="1">
-        <v>46043</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>46050</v>
-      </c>
-      <c r="F8" s="1">
-        <v>46043</v>
+        <v>46190</v>
       </c>
       <c r="G8" s="1">
-        <v>46050</v>
+        <v>46190</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1331,19 +1273,25 @@
         <v>26</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46051</v>
       </c>
       <c r="E9" s="1">
-        <v>46190</v>
+        <v>46058</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46051</v>
       </c>
       <c r="G9" s="1">
-        <v>46190</v>
+        <v>46058</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1372,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1383,19 +1331,25 @@
         <v>30</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D11" s="1">
-        <v>46043</v>
+        <v>46076</v>
+      </c>
+      <c r="E11" s="1">
+        <v>46087</v>
       </c>
       <c r="F11" s="1">
-        <v>46043</v>
+        <v>46076</v>
+      </c>
+      <c r="G11" s="1">
+        <v>46087</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1406,19 +1360,25 @@
         <v>32</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D12" s="1">
-        <v>46043</v>
+        <v>46059</v>
+      </c>
+      <c r="E12" s="1">
+        <v>46066</v>
       </c>
       <c r="F12" s="1">
-        <v>46043</v>
+        <v>46059</v>
+      </c>
+      <c r="G12" s="1">
+        <v>46066</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1429,19 +1389,25 @@
         <v>34</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D13" s="1">
-        <v>46043</v>
+        <v>46125</v>
+      </c>
+      <c r="E13" s="1">
+        <v>46132</v>
       </c>
       <c r="F13" s="1">
-        <v>46043</v>
+        <v>46125</v>
+      </c>
+      <c r="G13" s="1">
+        <v>46132</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1452,19 +1418,25 @@
         <v>36</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D14" s="1">
-        <v>46043</v>
+        <v>46051</v>
+      </c>
+      <c r="E14" s="1">
+        <v>46058</v>
       </c>
       <c r="F14" s="1">
-        <v>46043</v>
+        <v>46051</v>
+      </c>
+      <c r="G14" s="1">
+        <v>46058</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1475,19 +1447,25 @@
         <v>38</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D15" s="1">
-        <v>46043</v>
+        <v>46076</v>
+      </c>
+      <c r="E15" s="1">
+        <v>46105</v>
       </c>
       <c r="F15" s="1">
-        <v>46043</v>
+        <v>46076</v>
+      </c>
+      <c r="G15" s="1">
+        <v>46105</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1498,19 +1476,25 @@
         <v>40</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" s="1">
-        <v>46043</v>
+        <v>46126</v>
+      </c>
+      <c r="E16" s="1">
+        <v>46133</v>
       </c>
       <c r="F16" s="1">
-        <v>46043</v>
+        <v>46126</v>
+      </c>
+      <c r="G16" s="1">
+        <v>46133</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1521,19 +1505,25 @@
         <v>42</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D17" s="1">
-        <v>46043</v>
+        <v>46114</v>
+      </c>
+      <c r="E17" s="1">
+        <v>46125</v>
       </c>
       <c r="F17" s="1">
-        <v>46043</v>
+        <v>46114</v>
+      </c>
+      <c r="G17" s="1">
+        <v>46125</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1544,19 +1534,25 @@
         <v>44</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D18" s="1">
-        <v>46043</v>
+        <v>46106</v>
+      </c>
+      <c r="E18" s="1">
+        <v>46113</v>
       </c>
       <c r="F18" s="1">
-        <v>46043</v>
+        <v>46106</v>
+      </c>
+      <c r="G18" s="1">
+        <v>46113</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1567,19 +1563,25 @@
         <v>46</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D19" s="1">
-        <v>46043</v>
+        <v>46140</v>
+      </c>
+      <c r="E19" s="1">
+        <v>46148</v>
       </c>
       <c r="F19" s="1">
-        <v>46043</v>
+        <v>46140</v>
+      </c>
+      <c r="G19" s="1">
+        <v>46148</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1590,25 +1592,25 @@
         <v>48</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>46051</v>
+        <v>46043</v>
       </c>
       <c r="E20" s="1">
-        <v>46058</v>
+        <v>46048</v>
       </c>
       <c r="F20" s="1">
-        <v>46051</v>
+        <v>46043</v>
       </c>
       <c r="G20" s="1">
-        <v>46058</v>
+        <v>46048</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1619,25 +1621,25 @@
         <v>50</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D21" s="1">
-        <v>46076</v>
+        <v>46043</v>
       </c>
       <c r="E21" s="1">
-        <v>46087</v>
+        <v>46050</v>
       </c>
       <c r="F21" s="1">
-        <v>46076</v>
+        <v>46043</v>
       </c>
       <c r="G21" s="1">
-        <v>46087</v>
+        <v>46050</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1651,22 +1653,22 @@
         <v>6</v>
       </c>
       <c r="D22" s="1">
-        <v>46059</v>
+        <v>46136</v>
       </c>
       <c r="E22" s="1">
-        <v>46066</v>
+        <v>46143</v>
       </c>
       <c r="F22" s="1">
-        <v>46059</v>
+        <v>46136</v>
       </c>
       <c r="G22" s="1">
-        <v>46066</v>
+        <v>46143</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1680,22 +1682,22 @@
         <v>6</v>
       </c>
       <c r="D23" s="1">
-        <v>46125</v>
+        <v>46058</v>
       </c>
       <c r="E23" s="1">
-        <v>46132</v>
+        <v>46065</v>
       </c>
       <c r="F23" s="1">
-        <v>46125</v>
+        <v>46058</v>
       </c>
       <c r="G23" s="1">
-        <v>46132</v>
+        <v>46065</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1706,25 +1708,25 @@
         <v>56</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D24" s="1">
         <v>46051</v>
       </c>
       <c r="E24" s="1">
-        <v>46058</v>
+        <v>46065</v>
       </c>
       <c r="F24" s="1">
         <v>46051</v>
       </c>
       <c r="G24" s="1">
-        <v>46058</v>
+        <v>46065</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1735,25 +1737,25 @@
         <v>58</v>
       </c>
       <c r="C25">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D25" s="1">
-        <v>46076</v>
+        <v>46066</v>
       </c>
       <c r="E25" s="1">
-        <v>46105</v>
+        <v>46073</v>
       </c>
       <c r="F25" s="1">
-        <v>46076</v>
+        <v>46066</v>
       </c>
       <c r="G25" s="1">
-        <v>46105</v>
+        <v>46073</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1764,25 +1766,25 @@
         <v>60</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D26" s="1">
-        <v>46126</v>
+        <v>46113</v>
       </c>
       <c r="E26" s="1">
-        <v>46133</v>
+        <v>46129</v>
       </c>
       <c r="F26" s="1">
-        <v>46126</v>
+        <v>46113</v>
       </c>
       <c r="G26" s="1">
-        <v>46133</v>
+        <v>46129</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -1796,22 +1798,22 @@
         <v>6</v>
       </c>
       <c r="D27" s="1">
-        <v>46114</v>
+        <v>46132</v>
       </c>
       <c r="E27" s="1">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="F27" s="1">
-        <v>46114</v>
+        <v>46132</v>
       </c>
       <c r="G27" s="1">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
       <c r="I27">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -1822,25 +1824,25 @@
         <v>64</v>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D28" s="1">
         <v>46106</v>
       </c>
       <c r="E28" s="1">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="F28" s="1">
         <v>46106</v>
       </c>
       <c r="G28" s="1">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1854,22 +1856,22 @@
         <v>6</v>
       </c>
       <c r="D29" s="1">
-        <v>46140</v>
+        <v>46091</v>
       </c>
       <c r="E29" s="1">
-        <v>46148</v>
+        <v>46098</v>
       </c>
       <c r="F29" s="1">
-        <v>46140</v>
+        <v>46091</v>
       </c>
       <c r="G29" s="1">
-        <v>46148</v>
+        <v>46098</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="I29">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1880,25 +1882,25 @@
         <v>68</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="1">
-        <v>46043</v>
+        <v>46108</v>
       </c>
       <c r="E30" s="1">
-        <v>46048</v>
+        <v>46112</v>
       </c>
       <c r="F30" s="1">
-        <v>46043</v>
+        <v>46108</v>
       </c>
       <c r="G30" s="1">
-        <v>46048</v>
+        <v>46112</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>56</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1909,25 +1911,25 @@
         <v>70</v>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D31" s="1">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="E31" s="1">
-        <v>46050</v>
+        <v>46080</v>
       </c>
       <c r="F31" s="1">
-        <v>46043</v>
+        <v>46066</v>
       </c>
       <c r="G31" s="1">
-        <v>46050</v>
+        <v>46080</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>54</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1938,25 +1940,25 @@
         <v>72</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D32" s="1">
-        <v>46136</v>
+        <v>46066</v>
       </c>
       <c r="E32" s="1">
-        <v>46143</v>
+        <v>46080</v>
       </c>
       <c r="F32" s="1">
-        <v>46136</v>
+        <v>46066</v>
       </c>
       <c r="G32" s="1">
-        <v>46143</v>
+        <v>46080</v>
       </c>
       <c r="H32">
         <v>0</v>
       </c>
       <c r="I32">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -1970,22 +1972,22 @@
         <v>6</v>
       </c>
       <c r="D33" s="1">
-        <v>46058</v>
+        <v>46107</v>
       </c>
       <c r="E33" s="1">
-        <v>46065</v>
+        <v>46114</v>
       </c>
       <c r="F33" s="1">
-        <v>46058</v>
+        <v>46107</v>
       </c>
       <c r="G33" s="1">
-        <v>46065</v>
+        <v>46114</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -1996,25 +1998,25 @@
         <v>76</v>
       </c>
       <c r="C34">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D34" s="1">
-        <v>46051</v>
+        <v>46136</v>
       </c>
       <c r="E34" s="1">
-        <v>46065</v>
+        <v>46143</v>
       </c>
       <c r="F34" s="1">
-        <v>46051</v>
+        <v>46136</v>
       </c>
       <c r="G34" s="1">
-        <v>46065</v>
+        <v>46143</v>
       </c>
       <c r="H34">
         <v>0</v>
       </c>
       <c r="I34">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -2028,22 +2030,22 @@
         <v>6</v>
       </c>
       <c r="D35" s="1">
-        <v>46066</v>
+        <v>46107</v>
       </c>
       <c r="E35" s="1">
-        <v>46073</v>
+        <v>46114</v>
       </c>
       <c r="F35" s="1">
-        <v>46066</v>
+        <v>46107</v>
       </c>
       <c r="G35" s="1">
-        <v>46073</v>
+        <v>46114</v>
       </c>
       <c r="H35">
         <v>0</v>
       </c>
       <c r="I35">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -2054,25 +2056,25 @@
         <v>80</v>
       </c>
       <c r="C36">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D36" s="1">
-        <v>46113</v>
+        <v>46091</v>
       </c>
       <c r="E36" s="1">
-        <v>46129</v>
+        <v>46098</v>
       </c>
       <c r="F36" s="1">
-        <v>46113</v>
+        <v>46091</v>
       </c>
       <c r="G36" s="1">
-        <v>46129</v>
+        <v>46098</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
       <c r="I36">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -2086,22 +2088,22 @@
         <v>6</v>
       </c>
       <c r="D37" s="1">
-        <v>46132</v>
+        <v>46083</v>
       </c>
       <c r="E37" s="1">
-        <v>46139</v>
+        <v>46090</v>
       </c>
       <c r="F37" s="1">
-        <v>46132</v>
+        <v>46083</v>
       </c>
       <c r="G37" s="1">
-        <v>46139</v>
+        <v>46090</v>
       </c>
       <c r="H37">
         <v>0</v>
       </c>
       <c r="I37">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2112,25 +2114,25 @@
         <v>84</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D38" s="1">
+        <v>46099</v>
+      </c>
+      <c r="E38" s="1">
         <v>46106</v>
       </c>
-      <c r="E38" s="1">
-        <v>46107</v>
-      </c>
       <c r="F38" s="1">
+        <v>46099</v>
+      </c>
+      <c r="G38" s="1">
         <v>46106</v>
       </c>
-      <c r="G38" s="1">
-        <v>46107</v>
-      </c>
       <c r="H38">
         <v>0</v>
       </c>
       <c r="I38">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -2144,22 +2146,22 @@
         <v>6</v>
       </c>
       <c r="D39" s="1">
-        <v>46091</v>
+        <v>46136</v>
       </c>
       <c r="E39" s="1">
-        <v>46098</v>
+        <v>46143</v>
       </c>
       <c r="F39" s="1">
-        <v>46091</v>
+        <v>46136</v>
       </c>
       <c r="G39" s="1">
-        <v>46098</v>
+        <v>46143</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2170,25 +2172,25 @@
         <v>88</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40" s="1">
-        <v>46108</v>
+        <v>46126</v>
       </c>
       <c r="E40" s="1">
-        <v>46112</v>
+        <v>46129</v>
       </c>
       <c r="F40" s="1">
-        <v>46108</v>
+        <v>46126</v>
       </c>
       <c r="G40" s="1">
-        <v>46112</v>
+        <v>46129</v>
       </c>
       <c r="H40">
         <v>0</v>
       </c>
       <c r="I40">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -2199,25 +2201,25 @@
         <v>90</v>
       </c>
       <c r="C41">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D41" s="1">
-        <v>46066</v>
+        <v>46106</v>
       </c>
       <c r="E41" s="1">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="F41" s="1">
-        <v>46066</v>
+        <v>46106</v>
       </c>
       <c r="G41" s="1">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="H41">
         <v>0</v>
       </c>
       <c r="I41">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2228,25 +2230,25 @@
         <v>92</v>
       </c>
       <c r="C42">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D42" s="1">
-        <v>46066</v>
+        <v>46112</v>
       </c>
       <c r="E42" s="1">
-        <v>46080</v>
+        <v>46119</v>
       </c>
       <c r="F42" s="1">
-        <v>46066</v>
+        <v>46112</v>
       </c>
       <c r="G42" s="1">
-        <v>46080</v>
+        <v>46119</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
       <c r="I42">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -2257,25 +2259,25 @@
         <v>94</v>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D43" s="1">
-        <v>46107</v>
+        <v>46120</v>
       </c>
       <c r="E43" s="1">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="F43" s="1">
-        <v>46107</v>
+        <v>46120</v>
       </c>
       <c r="G43" s="1">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -2286,19 +2288,19 @@
         <v>96</v>
       </c>
       <c r="C44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D44" s="1">
-        <v>46136</v>
+        <v>46132</v>
       </c>
       <c r="E44" s="1">
-        <v>46143</v>
+        <v>46135</v>
       </c>
       <c r="F44" s="1">
-        <v>46136</v>
+        <v>46132</v>
       </c>
       <c r="G44" s="1">
-        <v>46143</v>
+        <v>46135</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -2315,25 +2317,25 @@
         <v>98</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D45" s="1">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="E45" s="1">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="F45" s="1">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="G45" s="1">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="H45">
         <v>0</v>
       </c>
       <c r="I45">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -2344,25 +2346,25 @@
         <v>100</v>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D46" s="1">
-        <v>46091</v>
+        <v>46132</v>
       </c>
       <c r="E46" s="1">
-        <v>46098</v>
+        <v>46147</v>
       </c>
       <c r="F46" s="1">
-        <v>46091</v>
+        <v>46132</v>
       </c>
       <c r="G46" s="1">
-        <v>46098</v>
+        <v>46147</v>
       </c>
       <c r="H46">
         <v>0</v>
       </c>
       <c r="I46">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -2376,22 +2378,22 @@
         <v>6</v>
       </c>
       <c r="D47" s="1">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="E47" s="1">
-        <v>46090</v>
+        <v>46098</v>
       </c>
       <c r="F47" s="1">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="G47" s="1">
-        <v>46090</v>
+        <v>46098</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
       <c r="I47">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -2402,25 +2404,25 @@
         <v>104</v>
       </c>
       <c r="C48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D48" s="1">
         <v>46099</v>
       </c>
       <c r="E48" s="1">
-        <v>46106</v>
+        <v>46104</v>
       </c>
       <c r="F48" s="1">
         <v>46099</v>
       </c>
       <c r="G48" s="1">
-        <v>46106</v>
+        <v>46104</v>
       </c>
       <c r="H48">
         <v>0</v>
       </c>
       <c r="I48">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -2434,22 +2436,22 @@
         <v>6</v>
       </c>
       <c r="D49" s="1">
-        <v>46136</v>
+        <v>46105</v>
       </c>
       <c r="E49" s="1">
-        <v>46143</v>
+        <v>46112</v>
       </c>
       <c r="F49" s="1">
-        <v>46136</v>
+        <v>46105</v>
       </c>
       <c r="G49" s="1">
-        <v>46143</v>
+        <v>46112</v>
       </c>
       <c r="H49">
         <v>0</v>
       </c>
       <c r="I49">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -2460,16 +2462,16 @@
         <v>108</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D50" s="1">
-        <v>46126</v>
+        <v>46113</v>
       </c>
       <c r="E50" s="1">
         <v>46129</v>
       </c>
       <c r="F50" s="1">
-        <v>46126</v>
+        <v>46113</v>
       </c>
       <c r="G50" s="1">
         <v>46129</v>
@@ -2478,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -2492,22 +2494,22 @@
         <v>4</v>
       </c>
       <c r="D51" s="1">
-        <v>46106</v>
+        <v>46099</v>
       </c>
       <c r="E51" s="1">
-        <v>46111</v>
+        <v>46104</v>
       </c>
       <c r="F51" s="1">
-        <v>46106</v>
+        <v>46099</v>
       </c>
       <c r="G51" s="1">
-        <v>46111</v>
+        <v>46104</v>
       </c>
       <c r="H51">
         <v>0</v>
       </c>
       <c r="I51">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2518,25 +2520,25 @@
         <v>112</v>
       </c>
       <c r="C52">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D52" s="1">
-        <v>46112</v>
+        <v>46076</v>
       </c>
       <c r="E52" s="1">
-        <v>46119</v>
+        <v>46090</v>
       </c>
       <c r="F52" s="1">
-        <v>46112</v>
+        <v>46076</v>
       </c>
       <c r="G52" s="1">
-        <v>46119</v>
+        <v>46090</v>
       </c>
       <c r="H52">
         <v>0</v>
       </c>
       <c r="I52">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -2547,25 +2549,25 @@
         <v>114</v>
       </c>
       <c r="C53">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D53" s="1">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="E53" s="1">
-        <v>46125</v>
+        <v>46122</v>
       </c>
       <c r="F53" s="1">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="G53" s="1">
-        <v>46125</v>
+        <v>46122</v>
       </c>
       <c r="H53">
         <v>0</v>
       </c>
       <c r="I53">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -2576,25 +2578,25 @@
         <v>116</v>
       </c>
       <c r="C54">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D54" s="1">
         <v>46132</v>
       </c>
       <c r="E54" s="1">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="F54" s="1">
         <v>46132</v>
       </c>
       <c r="G54" s="1">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="H54">
         <v>0</v>
       </c>
       <c r="I54">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -2605,25 +2607,25 @@
         <v>118</v>
       </c>
       <c r="C55">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D55" s="1">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="E55" s="1">
-        <v>46122</v>
+        <v>46112</v>
       </c>
       <c r="F55" s="1">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="G55" s="1">
-        <v>46122</v>
+        <v>46112</v>
       </c>
       <c r="H55">
         <v>0</v>
       </c>
       <c r="I55">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -2637,22 +2639,22 @@
         <v>11</v>
       </c>
       <c r="D56" s="1">
-        <v>46132</v>
+        <v>46149</v>
       </c>
       <c r="E56" s="1">
-        <v>46147</v>
+        <v>46163</v>
       </c>
       <c r="F56" s="1">
-        <v>46132</v>
+        <v>46149</v>
       </c>
       <c r="G56" s="1">
-        <v>46147</v>
+        <v>46163</v>
       </c>
       <c r="H56">
         <v>0</v>
       </c>
       <c r="I56">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -2663,25 +2665,19 @@
         <v>122</v>
       </c>
       <c r="C57">
-        <v>6</v>
-      </c>
-      <c r="D57" s="1">
-        <v>46091</v>
+        <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>46098</v>
-      </c>
-      <c r="F57" s="1">
-        <v>46091</v>
+        <v>46181</v>
       </c>
       <c r="G57" s="1">
-        <v>46098</v>
+        <v>46181</v>
       </c>
       <c r="H57">
         <v>0</v>
       </c>
       <c r="I57">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -2692,19 +2688,19 @@
         <v>124</v>
       </c>
       <c r="C58">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D58" s="1">
-        <v>46099</v>
+        <v>46164</v>
       </c>
       <c r="E58" s="1">
-        <v>46104</v>
+        <v>46181</v>
       </c>
       <c r="F58" s="1">
-        <v>46099</v>
+        <v>46164</v>
       </c>
       <c r="G58" s="1">
-        <v>46104</v>
+        <v>46181</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -2721,19 +2717,19 @@
         <v>126</v>
       </c>
       <c r="C59">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D59" s="1">
-        <v>46105</v>
+        <v>46149</v>
       </c>
       <c r="E59" s="1">
-        <v>46112</v>
+        <v>46149</v>
       </c>
       <c r="F59" s="1">
-        <v>46105</v>
+        <v>46149</v>
       </c>
       <c r="G59" s="1">
-        <v>46112</v>
+        <v>46149</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -2750,25 +2746,25 @@
         <v>128</v>
       </c>
       <c r="C60">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D60" s="1">
-        <v>46113</v>
+        <v>46043</v>
       </c>
       <c r="E60" s="1">
-        <v>46129</v>
+        <v>46072</v>
       </c>
       <c r="F60" s="1">
-        <v>46113</v>
+        <v>46043</v>
       </c>
       <c r="G60" s="1">
-        <v>46129</v>
+        <v>46072</v>
       </c>
       <c r="H60">
         <v>0</v>
       </c>
       <c r="I60">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -2779,25 +2775,25 @@
         <v>130</v>
       </c>
       <c r="C61">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D61" s="1">
-        <v>46099</v>
+        <v>46073</v>
       </c>
       <c r="E61" s="1">
-        <v>46104</v>
+        <v>46097</v>
       </c>
       <c r="F61" s="1">
-        <v>46099</v>
+        <v>46073</v>
       </c>
       <c r="G61" s="1">
-        <v>46104</v>
+        <v>46097</v>
       </c>
       <c r="H61">
         <v>0</v>
       </c>
       <c r="I61">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -2808,25 +2804,25 @@
         <v>132</v>
       </c>
       <c r="C62">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D62" s="1">
-        <v>46076</v>
+        <v>46098</v>
       </c>
       <c r="E62" s="1">
-        <v>46090</v>
+        <v>46104</v>
       </c>
       <c r="F62" s="1">
-        <v>46076</v>
+        <v>46098</v>
       </c>
       <c r="G62" s="1">
-        <v>46090</v>
+        <v>46104</v>
       </c>
       <c r="H62">
         <v>0</v>
       </c>
       <c r="I62">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -2837,25 +2833,25 @@
         <v>134</v>
       </c>
       <c r="C63">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D63" s="1">
-        <v>46113</v>
+        <v>46043</v>
       </c>
       <c r="E63" s="1">
-        <v>46122</v>
+        <v>46104</v>
       </c>
       <c r="F63" s="1">
-        <v>46113</v>
+        <v>46043</v>
       </c>
       <c r="G63" s="1">
-        <v>46122</v>
+        <v>46104</v>
       </c>
       <c r="H63">
         <v>0</v>
       </c>
       <c r="I63">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -2863,219 +2859,225 @@
         <v>135</v>
       </c>
       <c r="B64" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="C64">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D64" s="1">
-        <v>46132</v>
+        <v>46043</v>
       </c>
       <c r="E64" s="1">
-        <v>46139</v>
+        <v>46072</v>
       </c>
       <c r="F64" s="1">
-        <v>46132</v>
+        <v>46043</v>
       </c>
       <c r="G64" s="1">
-        <v>46139</v>
+        <v>46072</v>
       </c>
       <c r="H64">
         <v>0</v>
       </c>
       <c r="I64">
-        <v>19</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>136</v>
+      </c>
+      <c r="B65" t="s">
         <v>137</v>
-      </c>
-      <c r="B65" t="s">
-        <v>138</v>
       </c>
       <c r="C65">
         <v>6</v>
       </c>
       <c r="D65" s="1">
-        <v>46105</v>
+        <v>46086</v>
       </c>
       <c r="E65" s="1">
-        <v>46112</v>
+        <v>46093</v>
       </c>
       <c r="F65" s="1">
-        <v>46105</v>
+        <v>46086</v>
       </c>
       <c r="G65" s="1">
-        <v>46112</v>
+        <v>46093</v>
       </c>
       <c r="H65">
         <v>0</v>
       </c>
       <c r="I65">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>138</v>
+      </c>
+      <c r="B66" t="s">
         <v>139</v>
       </c>
-      <c r="B66" t="s">
-        <v>140</v>
-      </c>
       <c r="C66">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D66" s="1">
-        <v>46149</v>
+        <v>46105</v>
       </c>
       <c r="E66" s="1">
-        <v>46163</v>
+        <v>46112</v>
       </c>
       <c r="F66" s="1">
-        <v>46149</v>
+        <v>46105</v>
       </c>
       <c r="G66" s="1">
-        <v>46163</v>
+        <v>46112</v>
       </c>
       <c r="H66">
         <v>0</v>
       </c>
       <c r="I66">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" t="s">
         <v>141</v>
       </c>
-      <c r="B67" t="s">
-        <v>142</v>
-      </c>
       <c r="C67">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="D67" s="1">
+        <v>46113</v>
       </c>
       <c r="E67" s="1">
-        <v>46181</v>
+        <v>46121</v>
+      </c>
+      <c r="F67" s="1">
+        <v>46113</v>
       </c>
       <c r="G67" s="1">
-        <v>46181</v>
+        <v>46121</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>142</v>
+      </c>
+      <c r="B68" t="s">
         <v>143</v>
-      </c>
-      <c r="B68" t="s">
-        <v>144</v>
       </c>
       <c r="C68">
         <v>11</v>
       </c>
       <c r="D68" s="1">
-        <v>46164</v>
+        <v>46122</v>
       </c>
       <c r="E68" s="1">
-        <v>46181</v>
+        <v>46136</v>
       </c>
       <c r="F68" s="1">
-        <v>46164</v>
+        <v>46122</v>
       </c>
       <c r="G68" s="1">
-        <v>46181</v>
+        <v>46136</v>
       </c>
       <c r="H68">
         <v>0</v>
       </c>
       <c r="I68">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" t="s">
         <v>145</v>
       </c>
-      <c r="B69" t="s">
-        <v>146</v>
-      </c>
       <c r="C69">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D69" s="1">
-        <v>46149</v>
+        <v>46105</v>
       </c>
       <c r="E69" s="1">
-        <v>46149</v>
+        <v>46121</v>
       </c>
       <c r="F69" s="1">
-        <v>46149</v>
+        <v>46105</v>
       </c>
       <c r="G69" s="1">
-        <v>46149</v>
+        <v>46121</v>
       </c>
       <c r="H69">
         <v>0</v>
       </c>
       <c r="I69">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>146</v>
+      </c>
+      <c r="B70" t="s">
         <v>147</v>
       </c>
-      <c r="B70" t="s">
-        <v>148</v>
-      </c>
       <c r="C70">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D70" s="1">
-        <v>46043</v>
+        <v>46139</v>
       </c>
       <c r="E70" s="1">
-        <v>46072</v>
+        <v>46143</v>
       </c>
       <c r="F70" s="1">
-        <v>46043</v>
+        <v>46139</v>
       </c>
       <c r="G70" s="1">
-        <v>46072</v>
+        <v>46143</v>
       </c>
       <c r="H70">
         <v>0</v>
       </c>
       <c r="I70">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>148</v>
+      </c>
+      <c r="B71" t="s">
         <v>149</v>
       </c>
-      <c r="B71" t="s">
-        <v>150</v>
-      </c>
       <c r="C71">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D71" s="1">
-        <v>46073</v>
+        <v>46105</v>
       </c>
       <c r="E71" s="1">
-        <v>46097</v>
+        <v>46136</v>
       </c>
       <c r="F71" s="1">
-        <v>46073</v>
+        <v>46105</v>
       </c>
       <c r="G71" s="1">
-        <v>46097</v>
+        <v>46136</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -3086,25 +3088,25 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>150</v>
+      </c>
+      <c r="B72" t="s">
         <v>151</v>
-      </c>
-      <c r="B72" t="s">
-        <v>152</v>
       </c>
       <c r="C72">
         <v>5</v>
       </c>
       <c r="D72" s="1">
-        <v>46098</v>
+        <v>46154</v>
       </c>
       <c r="E72" s="1">
-        <v>46104</v>
+        <v>46160</v>
       </c>
       <c r="F72" s="1">
-        <v>46098</v>
+        <v>46154</v>
       </c>
       <c r="G72" s="1">
-        <v>46104</v>
+        <v>46160</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -3115,25 +3117,25 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>152</v>
+      </c>
+      <c r="B73" t="s">
         <v>153</v>
       </c>
-      <c r="B73" t="s">
-        <v>154</v>
-      </c>
       <c r="C73">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="D73" s="1">
-        <v>46043</v>
+        <v>46139</v>
       </c>
       <c r="E73" s="1">
-        <v>46104</v>
+        <v>46153</v>
       </c>
       <c r="F73" s="1">
-        <v>46043</v>
+        <v>46139</v>
       </c>
       <c r="G73" s="1">
-        <v>46104</v>
+        <v>46153</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -3144,31 +3146,31 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>154</v>
+      </c>
+      <c r="B74" t="s">
         <v>155</v>
       </c>
-      <c r="B74" t="s">
-        <v>52</v>
-      </c>
       <c r="C74">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D74" s="1">
         <v>46043</v>
       </c>
       <c r="E74" s="1">
-        <v>46072</v>
+        <v>46057</v>
       </c>
       <c r="F74" s="1">
         <v>46043</v>
       </c>
       <c r="G74" s="1">
-        <v>46072</v>
+        <v>46057</v>
       </c>
       <c r="H74">
         <v>0</v>
       </c>
       <c r="I74">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
@@ -3179,25 +3181,25 @@
         <v>157</v>
       </c>
       <c r="C75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D75" s="1">
-        <v>46086</v>
+        <v>46058</v>
       </c>
       <c r="E75" s="1">
-        <v>46093</v>
+        <v>46064</v>
       </c>
       <c r="F75" s="1">
-        <v>46086</v>
+        <v>46058</v>
       </c>
       <c r="G75" s="1">
-        <v>46093</v>
+        <v>46064</v>
       </c>
       <c r="H75">
         <v>0</v>
       </c>
       <c r="I75">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -3208,25 +3210,25 @@
         <v>159</v>
       </c>
       <c r="C76">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D76" s="1">
-        <v>46105</v>
+        <v>46142</v>
       </c>
       <c r="E76" s="1">
-        <v>46112</v>
+        <v>46183</v>
       </c>
       <c r="F76" s="1">
-        <v>46105</v>
+        <v>46142</v>
       </c>
       <c r="G76" s="1">
-        <v>46112</v>
+        <v>46183</v>
       </c>
       <c r="H76">
         <v>0</v>
       </c>
       <c r="I76">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -3240,22 +3242,22 @@
         <v>5</v>
       </c>
       <c r="D77" s="1">
-        <v>46113</v>
+        <v>46184</v>
       </c>
       <c r="E77" s="1">
-        <v>46121</v>
+        <v>46190</v>
       </c>
       <c r="F77" s="1">
-        <v>46113</v>
+        <v>46184</v>
       </c>
       <c r="G77" s="1">
-        <v>46121</v>
+        <v>46190</v>
       </c>
       <c r="H77">
         <v>0</v>
       </c>
       <c r="I77">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -3266,25 +3268,25 @@
         <v>163</v>
       </c>
       <c r="C78">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D78" s="1">
-        <v>46122</v>
+        <v>46142</v>
       </c>
       <c r="E78" s="1">
-        <v>46136</v>
+        <v>46183</v>
       </c>
       <c r="F78" s="1">
-        <v>46122</v>
+        <v>46142</v>
       </c>
       <c r="G78" s="1">
-        <v>46136</v>
+        <v>46183</v>
       </c>
       <c r="H78">
         <v>0</v>
       </c>
       <c r="I78">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -3295,25 +3297,25 @@
         <v>165</v>
       </c>
       <c r="C79">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D79" s="1">
-        <v>46105</v>
+        <v>46006</v>
       </c>
       <c r="E79" s="1">
-        <v>46121</v>
+        <v>46049</v>
       </c>
       <c r="F79" s="1">
-        <v>46105</v>
+        <v>46006</v>
       </c>
       <c r="G79" s="1">
-        <v>46121</v>
+        <v>46049</v>
       </c>
       <c r="H79">
         <v>0</v>
       </c>
       <c r="I79">
-        <v>44</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -3324,25 +3326,19 @@
         <v>167</v>
       </c>
       <c r="C80">
-        <v>5</v>
-      </c>
-      <c r="D80" s="1">
-        <v>46139</v>
+        <v>0</v>
       </c>
       <c r="E80" s="1">
-        <v>46143</v>
-      </c>
-      <c r="F80" s="1">
-        <v>46139</v>
+        <v>46049</v>
       </c>
       <c r="G80" s="1">
-        <v>46143</v>
+        <v>46049</v>
       </c>
       <c r="H80">
         <v>0</v>
       </c>
       <c r="I80">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
@@ -3353,25 +3349,19 @@
         <v>169</v>
       </c>
       <c r="C81">
-        <v>22</v>
-      </c>
-      <c r="D81" s="1">
-        <v>46105</v>
+        <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>46136</v>
-      </c>
-      <c r="F81" s="1">
-        <v>46105</v>
+        <v>46175</v>
       </c>
       <c r="G81" s="1">
-        <v>46136</v>
+        <v>46175</v>
       </c>
       <c r="H81">
         <v>0</v>
       </c>
       <c r="I81">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -3382,25 +3372,25 @@
         <v>171</v>
       </c>
       <c r="C82">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D82" s="1">
-        <v>46154</v>
+        <v>46050</v>
       </c>
       <c r="E82" s="1">
-        <v>46160</v>
+        <v>46057</v>
       </c>
       <c r="F82" s="1">
-        <v>46154</v>
+        <v>46050</v>
       </c>
       <c r="G82" s="1">
-        <v>46160</v>
+        <v>46057</v>
       </c>
       <c r="H82">
         <v>0</v>
       </c>
       <c r="I82">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -3411,25 +3401,25 @@
         <v>173</v>
       </c>
       <c r="C83">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D83" s="1">
-        <v>46139</v>
+        <v>46058</v>
       </c>
       <c r="E83" s="1">
-        <v>46153</v>
+        <v>46099</v>
       </c>
       <c r="F83" s="1">
-        <v>46139</v>
+        <v>46058</v>
       </c>
       <c r="G83" s="1">
-        <v>46153</v>
+        <v>46099</v>
       </c>
       <c r="H83">
         <v>0</v>
       </c>
       <c r="I83">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -3440,25 +3430,25 @@
         <v>175</v>
       </c>
       <c r="C84">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D84" s="1">
-        <v>46043</v>
+        <v>46142</v>
       </c>
       <c r="E84" s="1">
-        <v>46057</v>
+        <v>46156</v>
       </c>
       <c r="F84" s="1">
-        <v>46043</v>
+        <v>46142</v>
       </c>
       <c r="G84" s="1">
-        <v>46057</v>
+        <v>46156</v>
       </c>
       <c r="H84">
         <v>0</v>
       </c>
       <c r="I84">
-        <v>65</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
@@ -3469,25 +3459,25 @@
         <v>177</v>
       </c>
       <c r="C85">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D85" s="1">
-        <v>46058</v>
+        <v>46168</v>
       </c>
       <c r="E85" s="1">
-        <v>46064</v>
+        <v>46175</v>
       </c>
       <c r="F85" s="1">
-        <v>46058</v>
+        <v>46168</v>
       </c>
       <c r="G85" s="1">
-        <v>46064</v>
+        <v>46175</v>
       </c>
       <c r="H85">
         <v>0</v>
       </c>
       <c r="I85">
-        <v>65</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -3498,25 +3488,25 @@
         <v>179</v>
       </c>
       <c r="C86">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D86" s="1">
-        <v>46142</v>
+        <v>46157</v>
       </c>
       <c r="E86" s="1">
-        <v>46183</v>
+        <v>46164</v>
       </c>
       <c r="F86" s="1">
-        <v>46142</v>
+        <v>46157</v>
       </c>
       <c r="G86" s="1">
-        <v>46183</v>
+        <v>46164</v>
       </c>
       <c r="H86">
         <v>0</v>
       </c>
       <c r="I86">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -3527,19 +3517,19 @@
         <v>181</v>
       </c>
       <c r="C87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D87" s="1">
-        <v>46184</v>
+        <v>46134</v>
       </c>
       <c r="E87" s="1">
-        <v>46190</v>
+        <v>46141</v>
       </c>
       <c r="F87" s="1">
-        <v>46184</v>
+        <v>46134</v>
       </c>
       <c r="G87" s="1">
-        <v>46190</v>
+        <v>46141</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -3556,19 +3546,19 @@
         <v>183</v>
       </c>
       <c r="C88">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D88" s="1">
-        <v>46142</v>
+        <v>46107</v>
       </c>
       <c r="E88" s="1">
-        <v>46183</v>
+        <v>46133</v>
       </c>
       <c r="F88" s="1">
-        <v>46142</v>
+        <v>46107</v>
       </c>
       <c r="G88" s="1">
-        <v>46183</v>
+        <v>46133</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -3585,25 +3575,25 @@
         <v>185</v>
       </c>
       <c r="C89">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D89" s="1">
-        <v>46006</v>
+        <v>46176</v>
       </c>
       <c r="E89" s="1">
-        <v>46049</v>
+        <v>46177</v>
       </c>
       <c r="F89" s="1">
-        <v>46006</v>
+        <v>46176</v>
       </c>
       <c r="G89" s="1">
-        <v>46049</v>
+        <v>46177</v>
       </c>
       <c r="H89">
         <v>0</v>
       </c>
       <c r="I89">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -3617,10 +3607,10 @@
         <v>0</v>
       </c>
       <c r="E90" s="1">
-        <v>46049</v>
+        <v>46099</v>
       </c>
       <c r="G90" s="1">
-        <v>46049</v>
+        <v>46099</v>
       </c>
       <c r="H90">
         <v>0</v>
@@ -3640,16 +3630,16 @@
         <v>0</v>
       </c>
       <c r="E91" s="1">
-        <v>46175</v>
+        <v>46099</v>
       </c>
       <c r="G91" s="1">
-        <v>46175</v>
+        <v>46099</v>
       </c>
       <c r="H91">
         <v>0</v>
       </c>
       <c r="I91">
-        <v>23</v>
+        <v>68</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -3660,17 +3650,11 @@
         <v>191</v>
       </c>
       <c r="C92">
-        <v>6</v>
-      </c>
-      <c r="D92" s="1">
-        <v>46050</v>
+        <v>0</v>
       </c>
       <c r="E92" s="1">
         <v>46057</v>
       </c>
-      <c r="F92" s="1">
-        <v>46050</v>
-      </c>
       <c r="G92" s="1">
         <v>46057</v>
       </c>
@@ -3678,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -3689,25 +3673,19 @@
         <v>193</v>
       </c>
       <c r="C93">
-        <v>30</v>
-      </c>
-      <c r="D93" s="1">
-        <v>46058</v>
+        <v>0</v>
       </c>
       <c r="E93" s="1">
-        <v>46099</v>
-      </c>
-      <c r="F93" s="1">
-        <v>46058</v>
+        <v>46065</v>
       </c>
       <c r="G93" s="1">
-        <v>46099</v>
+        <v>46065</v>
       </c>
       <c r="H93">
         <v>0</v>
       </c>
       <c r="I93">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -3718,19 +3696,13 @@
         <v>195</v>
       </c>
       <c r="C94">
-        <v>10</v>
-      </c>
-      <c r="D94" s="1">
-        <v>46142</v>
+        <v>0</v>
       </c>
       <c r="E94" s="1">
-        <v>46156</v>
-      </c>
-      <c r="F94" s="1">
-        <v>46142</v>
+        <v>46099</v>
       </c>
       <c r="G94" s="1">
-        <v>46156</v>
+        <v>46099</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -3747,25 +3719,25 @@
         <v>197</v>
       </c>
       <c r="C95">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D95" s="1">
-        <v>46168</v>
+        <v>46100</v>
       </c>
       <c r="E95" s="1">
-        <v>46175</v>
+        <v>46106</v>
       </c>
       <c r="F95" s="1">
-        <v>46168</v>
+        <v>46100</v>
       </c>
       <c r="G95" s="1">
-        <v>46175</v>
+        <v>46106</v>
       </c>
       <c r="H95">
         <v>0</v>
       </c>
       <c r="I95">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -3776,25 +3748,25 @@
         <v>199</v>
       </c>
       <c r="C96">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D96" s="1">
-        <v>46157</v>
+        <v>46100</v>
       </c>
       <c r="E96" s="1">
-        <v>46164</v>
+        <v>46106</v>
       </c>
       <c r="F96" s="1">
-        <v>46157</v>
+        <v>46100</v>
       </c>
       <c r="G96" s="1">
-        <v>46164</v>
+        <v>46106</v>
       </c>
       <c r="H96">
         <v>0</v>
       </c>
       <c r="I96">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
@@ -3805,25 +3777,25 @@
         <v>201</v>
       </c>
       <c r="C97">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D97" s="1">
-        <v>46134</v>
+        <v>46058</v>
       </c>
       <c r="E97" s="1">
-        <v>46141</v>
+        <v>46064</v>
       </c>
       <c r="F97" s="1">
-        <v>46134</v>
+        <v>46058</v>
       </c>
       <c r="G97" s="1">
-        <v>46141</v>
+        <v>46064</v>
       </c>
       <c r="H97">
         <v>0</v>
       </c>
       <c r="I97">
-        <v>12</v>
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -3834,25 +3806,25 @@
         <v>203</v>
       </c>
       <c r="C98">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D98" s="1">
-        <v>46107</v>
+        <v>46066</v>
       </c>
       <c r="E98" s="1">
-        <v>46133</v>
+        <v>46072</v>
       </c>
       <c r="F98" s="1">
-        <v>46107</v>
+        <v>46066</v>
       </c>
       <c r="G98" s="1">
-        <v>46133</v>
+        <v>46072</v>
       </c>
       <c r="H98">
         <v>0</v>
       </c>
       <c r="I98">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -3863,284 +3835,24 @@
         <v>205</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D99" s="1">
-        <v>46176</v>
+        <v>46100</v>
       </c>
       <c r="E99" s="1">
-        <v>46177</v>
+        <v>46106</v>
       </c>
       <c r="F99" s="1">
-        <v>46176</v>
+        <v>46100</v>
       </c>
       <c r="G99" s="1">
-        <v>46177</v>
+        <v>46106</v>
       </c>
       <c r="H99">
         <v>0</v>
       </c>
       <c r="I99">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>206</v>
-      </c>
-      <c r="B100" t="s">
-        <v>207</v>
-      </c>
-      <c r="C100">
-        <v>0</v>
-      </c>
-      <c r="E100" s="1">
-        <v>46099</v>
-      </c>
-      <c r="G100" s="1">
-        <v>46099</v>
-      </c>
-      <c r="H100">
-        <v>0</v>
-      </c>
-      <c r="I100">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>208</v>
-      </c>
-      <c r="B101" t="s">
-        <v>209</v>
-      </c>
-      <c r="C101">
-        <v>0</v>
-      </c>
-      <c r="E101" s="1">
-        <v>46099</v>
-      </c>
-      <c r="G101" s="1">
-        <v>46099</v>
-      </c>
-      <c r="H101">
-        <v>0</v>
-      </c>
-      <c r="I101">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>210</v>
-      </c>
-      <c r="B102" t="s">
-        <v>211</v>
-      </c>
-      <c r="C102">
-        <v>0</v>
-      </c>
-      <c r="E102" s="1">
-        <v>46057</v>
-      </c>
-      <c r="G102" s="1">
-        <v>46057</v>
-      </c>
-      <c r="H102">
-        <v>0</v>
-      </c>
-      <c r="I102">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>212</v>
-      </c>
-      <c r="B103" t="s">
-        <v>213</v>
-      </c>
-      <c r="C103">
-        <v>0</v>
-      </c>
-      <c r="E103" s="1">
-        <v>46065</v>
-      </c>
-      <c r="G103" s="1">
-        <v>46065</v>
-      </c>
-      <c r="H103">
-        <v>0</v>
-      </c>
-      <c r="I103">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>214</v>
-      </c>
-      <c r="B104" t="s">
-        <v>215</v>
-      </c>
-      <c r="C104">
-        <v>0</v>
-      </c>
-      <c r="E104" s="1">
-        <v>46099</v>
-      </c>
-      <c r="G104" s="1">
-        <v>46099</v>
-      </c>
-      <c r="H104">
-        <v>0</v>
-      </c>
-      <c r="I104">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>216</v>
-      </c>
-      <c r="B105" t="s">
-        <v>217</v>
-      </c>
-      <c r="C105">
-        <v>5</v>
-      </c>
-      <c r="D105" s="1">
-        <v>46100</v>
-      </c>
-      <c r="E105" s="1">
-        <v>46106</v>
-      </c>
-      <c r="F105" s="1">
-        <v>46100</v>
-      </c>
-      <c r="G105" s="1">
-        <v>46106</v>
-      </c>
-      <c r="H105">
-        <v>0</v>
-      </c>
-      <c r="I105">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>218</v>
-      </c>
-      <c r="B106" t="s">
-        <v>219</v>
-      </c>
-      <c r="C106">
-        <v>5</v>
-      </c>
-      <c r="D106" s="1">
-        <v>46100</v>
-      </c>
-      <c r="E106" s="1">
-        <v>46106</v>
-      </c>
-      <c r="F106" s="1">
-        <v>46100</v>
-      </c>
-      <c r="G106" s="1">
-        <v>46106</v>
-      </c>
-      <c r="H106">
-        <v>0</v>
-      </c>
-      <c r="I106">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>220</v>
-      </c>
-      <c r="B107" t="s">
-        <v>221</v>
-      </c>
-      <c r="C107">
-        <v>5</v>
-      </c>
-      <c r="D107" s="1">
-        <v>46058</v>
-      </c>
-      <c r="E107" s="1">
-        <v>46064</v>
-      </c>
-      <c r="F107" s="1">
-        <v>46058</v>
-      </c>
-      <c r="G107" s="1">
-        <v>46064</v>
-      </c>
-      <c r="H107">
-        <v>0</v>
-      </c>
-      <c r="I107">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>222</v>
-      </c>
-      <c r="B108" t="s">
-        <v>223</v>
-      </c>
-      <c r="C108">
-        <v>5</v>
-      </c>
-      <c r="D108" s="1">
-        <v>46066</v>
-      </c>
-      <c r="E108" s="1">
-        <v>46072</v>
-      </c>
-      <c r="F108" s="1">
-        <v>46066</v>
-      </c>
-      <c r="G108" s="1">
-        <v>46072</v>
-      </c>
-      <c r="H108">
-        <v>0</v>
-      </c>
-      <c r="I108">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>224</v>
-      </c>
-      <c r="B109" t="s">
-        <v>225</v>
-      </c>
-      <c r="C109">
-        <v>5</v>
-      </c>
-      <c r="D109" s="1">
-        <v>46100</v>
-      </c>
-      <c r="E109" s="1">
-        <v>46106</v>
-      </c>
-      <c r="F109" s="1">
-        <v>46100</v>
-      </c>
-      <c r="G109" s="1">
-        <v>46106</v>
-      </c>
-      <c r="H109">
-        <v>0</v>
-      </c>
-      <c r="I109">
         <v>12</v>
       </c>
     </row>
